--- a/files/Target_Financials_3Y.xlsx
+++ b/files/Target_Financials_3Y.xlsx
@@ -7,9 +7,19 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3Y Financials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QoE Adjustments" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'P&amp;L'!$A$1:$G$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Balance Sheet'!$A$1:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cash Flow'!$A$1:$D$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'KPIs'!$A$1:$E$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'QoE Adjustments'!$A$1:$D$10</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,23 +36,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Aptos"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -51,12 +51,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="000F4C81"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,30 +65,30 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D1D5DB"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D1D5DB"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D1D5DB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D1D5DB"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,358 +454,1941 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>M&amp;A Target - 3 Year Financials (MYR)</t>
+          <t>MYR M</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY2023A</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY2024A</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY2025A</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>FY2026F (Mgmt)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>FY2027F (Mgmt)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Auditor Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>482.4</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>531.0</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>602.8</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>670.2</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>744.6</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Growth +10% CAGR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>(289.4)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>(312.8)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>(355.6)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>(394.1)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>(434.6)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>GM stable ~40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>193.0</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>218.2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>247.2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>276.1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>310.0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>(138.5)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>(146.2)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>(164.1)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>(180.5)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>(199.6)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83.1</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>95.6</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>110.4</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Margin trending 14-16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; amortisation</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>(18.4)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>(20.1)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>(22.8)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>(25.6)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>(28.0)</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>36.1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Net interest</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>(7.2)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>(8.5)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>(9.8)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>(10.5)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>(11.2)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Profit before tax</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>28.9</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>43.4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>50.5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>59.5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Income tax</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>(6.9)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>(10.4)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>(12.1)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>(14.3)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>(17.1)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>24% effective rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>38.4</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>45.2</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G12"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MYR M</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY2023A</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>FY2024A</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY2025A</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Auditor Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Cash &amp; equivalents</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>62.4</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>71.8</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Trade receivables</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>71.5</t>
+        </is>
+      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>78.6</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>89.1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>DSO 54 days — trending up</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>38.4</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47.6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Other current assets</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>12.4</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Total current assets</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>170.5</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>197.3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>224.5</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>PP&amp;E (net)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>148.6</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>167.4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>184.2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Capex ~7% of revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; intangibles</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>62.1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>62.1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>62.1</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>From 2018 acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Other non-current</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>17.4</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Total non-current</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>224.9</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>245.3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>263.7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL ASSETS</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>395.4</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>442.6</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>488.2</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Trade payables</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>63.9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>71.2</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Short-term debt</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>34.8</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Other current liabilities</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>25.1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>28.4</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Total current liabilities</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>115.8</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>127.2</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>140.6</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Long-term debt</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>78.4</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>82.1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Lender covenants — see register</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Other non-current</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>18.6</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Total non-current liabilities</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>102.2</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>111.5</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>182.6</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>213.2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>236.1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL EQUITY + LIABILITIES</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>395.4</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>442.6</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>488.2</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E20"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MYR M</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY2023A</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY2024A</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>FY2025A</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>83.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Changes in working capital</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>(8.2)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>(11.4)</t>
+        </is>
+      </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>FY2026E</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>CAGR</t>
+          <t>(14.6)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>318,200,000</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>358,400,000</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>392,800,000</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>11.0%</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Cash from operations</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>68.5</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>86,400,000</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>99,800,000</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>112,400,000</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>14.0%</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Capex (maintenance)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>(18.4)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>(22.1)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>(24.8)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>27.2%</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>27.8%</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Capex (growth)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>(14.2)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>(18.5)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>(22.0)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Opex</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>42,800,000</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>47,200,000</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>51,300,000</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>9.5%</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21.7</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>43,600,000</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>52,600,000</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>61,100,000</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>18.4%</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Net interest paid</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>(7.2)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>(8.5)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>(9.8)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>EBITDA margin</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>13.7%</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>14.7%</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>15.6%</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Tax paid</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>(6.9)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>(10.4)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>(12.1)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>9,800,000</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>11,200,000</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>12,400,000</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Cash flow before financing</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>(0.4)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>(0.2)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>33,800,000</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>41,400,000</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>48,700,000</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>20.0%</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Net debt drawdown / (repayment)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7.4</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Net interest</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>4,800,000</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>5,200,000</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>4,800,000</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Dividends paid</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>(4.8)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>(6.2)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>(7.2)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>PBT</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>29,000,000</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>36,200,000</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>43,900,000</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>23.0%</t>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Net change in cash</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>(1.4)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D13"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY2023A</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY2024A</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY2025A</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Revenue growth %</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>10.1%</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>41.1%</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>41.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>EBITDA margin %</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>11.3%</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>13.6%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>EBIT margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>9.8%</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Net margin %</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>4.6%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>6.2%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>DSO (days)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>DIO (days)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>DPO (days)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Cash conversion cycle (days)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1.20x</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0.80x</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0.71x</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Net debt (MYR M)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>57.9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>58.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ROIC</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>9.8%</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Tax</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>7,300,000</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>9,100,000</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>11,000,000</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Customer concentration: top-3</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Trending — top customer now 14%</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>PAT</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>21,700,000</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>27,100,000</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>32,900,000</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>23.1%</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Customer concentration: top-10</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Trending — risk increasing</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
+  <autoFilter ref="A1:E15"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>MYR M</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Auditor Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>FY2025 reported EBITDA</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>83.1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Adj: One-time legal settlement</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>+2.4</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Add-back</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Single litigation matter (settled 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Adj: COVID-recovery grants</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>-1.8</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Remove</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Non-recurring government support</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Adj: Owner remuneration above market</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>+3.2</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Add-back</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>To be normalised at market rate post-deal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Adj: Related-party rent below market</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Deduct</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Lease to be revised at market post-deal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Adj: R&amp;D capitalisation review</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>-0.9</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Deduct</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Software development costs over-capitalised</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Adj: Inventory write-down (one-off)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>+1.1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Add-back</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Discontinued SKU clear-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Adjusted FY2025 EBITDA</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Pro-forma normalised</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>EV / EBITDA at offer price (8.5x)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>728.5</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Implied enterprise value at offer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>